--- a/NEGOCIO.xlsx
+++ b/NEGOCIO.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="54">
   <si>
     <t>Key</t>
   </si>
@@ -45,6 +45,21 @@
     <t>Fotos</t>
   </si>
   <si>
+    <t>Marca</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Condición</t>
+  </si>
+  <si>
+    <t>cantidad</t>
+  </si>
+  <si>
+    <t>ubicación</t>
+  </si>
+  <si>
     <t>Descripción AB</t>
   </si>
   <si>
@@ -54,13 +69,10 @@
     <t>Fecha Venta</t>
   </si>
   <si>
-    <t>Vendido En</t>
-  </si>
-  <si>
     <t>PROD-001</t>
   </si>
   <si>
-    <t>Audífonos Bluetooth Pro ANC</t>
+    <t>Audífonos Bluetooth Pro</t>
   </si>
   <si>
     <t>$120.000</t>
@@ -84,19 +96,37 @@
     <t/>
   </si>
   <si>
-    <t>Audífonos inalámbricos con cancelación activa de ruido.</t>
+    <t>AudioBrand</t>
+  </si>
+  <si>
+    <t>Accesorios</t>
+  </si>
+  <si>
+    <t>Nuevo</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Bodega Principal A-1</t>
+  </si>
+  <si>
+    <t>Audífonos inalámbricos de alta fidelidad con cancelación de ruido</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
   </si>
   <si>
     <t>PROD-002</t>
   </si>
   <si>
-    <t>Reloj Inteligente Sport GPS</t>
+    <t>Smartwatch Sport</t>
   </si>
   <si>
     <t>$250.000</t>
   </si>
   <si>
-    <t>$210.000</t>
+    <t>$200.000</t>
   </si>
   <si>
     <t>$150.000</t>
@@ -108,7 +138,25 @@
     <t>66,7%</t>
   </si>
   <si>
-    <t>Smartwatch con monitor cardíaco y resistencia 5 ATM.</t>
+    <t>TechTime</t>
+  </si>
+  <si>
+    <t>Relojes</t>
+  </si>
+  <si>
+    <t>Reacondicionado</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Estante B-3</t>
+  </si>
+  <si>
+    <t>Reloj inteligente con monitor cardíaco y GPS</t>
+  </si>
+  <si>
+    <t>2026-02-01</t>
   </si>
   <si>
     <t>Condiciones</t>
@@ -120,16 +168,10 @@
     <t>Canales</t>
   </si>
   <si>
-    <t>Nuevo</t>
-  </si>
-  <si>
     <t>Comprado</t>
   </si>
   <si>
     <t>shopify</t>
-  </si>
-  <si>
-    <t>Reacondicionado</t>
   </si>
   <si>
     <t>meta_catalogo</t>
@@ -177,7 +219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -223,93 +265,129 @@
       <c r="N1" t="s" s="0">
         <v>13</v>
       </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s" s="0">
+        <v>17</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s" s="0">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L2" t="s" s="0">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="M2" t="s" s="0">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="N2" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="O2" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="P2" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="R2" t="s" s="0">
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="H3" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>21</v>
-      </c>
       <c r="I3" t="s" s="0">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s" s="0">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="M3" t="s" s="0">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s" s="0">
-        <v>22</v>
+        <v>44</v>
+      </c>
+      <c r="O3" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="P3" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="Q3" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="R3" t="s" s="0">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -324,35 +402,35 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>37</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>39</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
